--- a/week-1/Exercise 5.B Lola's Kitchen - Customer Feedback .xlsx
+++ b/week-1/Exercise 5.B Lola's Kitchen - Customer Feedback .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yanuriscampusano\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yanuriscampusano\Documents\DataAnalytics\week-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DB95C24-C42A-469B-A530-0DD04FB5DE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47201FC4-80B0-439E-92E8-A2D81361A1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="19" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -150,7 +150,7 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Count of How often do you visit Lola's kitchen? </t>
+    <t>Sum of How would you rate your overall experience today?</t>
   </si>
 </sst>
 </file>
@@ -159,7 +159,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -216,8 +216,7 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="45" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -225,7 +224,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -271,10 +271,10 @@
       <numFmt numFmtId="28" formatCode="mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -389,28 +389,6 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent6"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
           <c:dLblPos val="inEnd"/>
@@ -443,17 +421,245 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="5"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="18"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="19"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="20"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent6"/>
           </a:solidFill>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -486,347 +692,12 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent6"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="7"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent6"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="8"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent6"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="9"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent6"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="10"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent6"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="11"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent6"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
@@ -836,10 +707,8 @@
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -854,170 +723,164 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-            <a:ln>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:shade val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:tint val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
               <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet3!$A$2:$A$4</c:f>
+              <c:f>Sheet3!$A$2:$A$5</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>Monthly</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>This Is My First Visit</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Weekly</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet3!$B$2:$B$4</c:f>
+              <c:f>Sheet3!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-E93B-49A4-90FD-46DE2D1BF47C}"/>
+              <c16:uniqueId val="{00000009-C272-469A-927A-CC83E5D8CD92}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:axId val="1679843407"/>
-        <c:axId val="1679852047"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1679843407"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1679852047"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1679852047"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1679843407"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1124,7 +987,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1181,7 +1044,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -1232,6 +1095,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1242,12 +1112,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -1285,7 +1162,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -1328,22 +1205,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1448,8 +1326,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1581,19 +1459,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1672,18 +1551,26 @@
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
-  <cacheFields count="16">
+  <cacheFields count="19">
     <cacheField name="ID" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="6"/>
     </cacheField>
-    <cacheField name="Start time" numFmtId="166">
+    <cacheField name="Start time" numFmtId="165">
       <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-04-09T08:42:27" maxDate="2026-04-12T07:30:59"/>
     </cacheField>
-    <cacheField name="Completion time" numFmtId="166">
+    <cacheField name="Completion time" numFmtId="165">
       <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-04-09T08:43:07" maxDate="2026-04-12T07:31:47"/>
     </cacheField>
     <cacheField name="Time to complete" numFmtId="45">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="1899-12-30T00:00:38" maxDate="1899-12-30T00:04:12"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="1899-12-30T00:00:38" maxDate="1899-12-30T00:04:12" count="6">
+        <d v="1899-12-30T00:00:40"/>
+        <d v="1899-12-30T00:02:46"/>
+        <d v="1899-12-30T00:01:49"/>
+        <d v="1899-12-30T00:04:12"/>
+        <d v="1899-12-30T00:00:38"/>
+        <d v="1899-12-30T00:00:48"/>
+      </sharedItems>
+      <fieldGroup par="18"/>
     </cacheField>
     <cacheField name="Email" numFmtId="0">
       <sharedItems containsBlank="1" count="2">
@@ -1692,7 +1579,9 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Name" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Last modified time" numFmtId="164">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -1748,6 +1637,177 @@
     <cacheField name="Is there anything we could improve or that you would like to see on the menu?" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
+    <cacheField name="Seconds (Time to complete)" numFmtId="0" databaseField="0">
+      <fieldGroup base="3">
+        <rangePr groupBy="seconds" startDate="1899-12-30T00:00:38" endDate="1899-12-30T00:04:12"/>
+        <groupItems count="62">
+          <s v="&lt;1/0/1900"/>
+          <s v=":00"/>
+          <s v=":01"/>
+          <s v=":02"/>
+          <s v=":03"/>
+          <s v=":04"/>
+          <s v=":05"/>
+          <s v=":06"/>
+          <s v=":07"/>
+          <s v=":08"/>
+          <s v=":09"/>
+          <s v=":10"/>
+          <s v=":11"/>
+          <s v=":12"/>
+          <s v=":13"/>
+          <s v=":14"/>
+          <s v=":15"/>
+          <s v=":16"/>
+          <s v=":17"/>
+          <s v=":18"/>
+          <s v=":19"/>
+          <s v=":20"/>
+          <s v=":21"/>
+          <s v=":22"/>
+          <s v=":23"/>
+          <s v=":24"/>
+          <s v=":25"/>
+          <s v=":26"/>
+          <s v=":27"/>
+          <s v=":28"/>
+          <s v=":29"/>
+          <s v=":30"/>
+          <s v=":31"/>
+          <s v=":32"/>
+          <s v=":33"/>
+          <s v=":34"/>
+          <s v=":35"/>
+          <s v=":36"/>
+          <s v=":37"/>
+          <s v=":38"/>
+          <s v=":39"/>
+          <s v=":40"/>
+          <s v=":41"/>
+          <s v=":42"/>
+          <s v=":43"/>
+          <s v=":44"/>
+          <s v=":45"/>
+          <s v=":46"/>
+          <s v=":47"/>
+          <s v=":48"/>
+          <s v=":49"/>
+          <s v=":50"/>
+          <s v=":51"/>
+          <s v=":52"/>
+          <s v=":53"/>
+          <s v=":54"/>
+          <s v=":55"/>
+          <s v=":56"/>
+          <s v=":57"/>
+          <s v=":58"/>
+          <s v=":59"/>
+          <s v="&gt;1/0/1900"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Minutes (Time to complete)" numFmtId="0" databaseField="0">
+      <fieldGroup base="3">
+        <rangePr groupBy="minutes" startDate="1899-12-30T00:00:38" endDate="1899-12-30T00:04:12"/>
+        <groupItems count="62">
+          <s v="&lt;1/0/1900"/>
+          <s v=":00"/>
+          <s v=":01"/>
+          <s v=":02"/>
+          <s v=":03"/>
+          <s v=":04"/>
+          <s v=":05"/>
+          <s v=":06"/>
+          <s v=":07"/>
+          <s v=":08"/>
+          <s v=":09"/>
+          <s v=":10"/>
+          <s v=":11"/>
+          <s v=":12"/>
+          <s v=":13"/>
+          <s v=":14"/>
+          <s v=":15"/>
+          <s v=":16"/>
+          <s v=":17"/>
+          <s v=":18"/>
+          <s v=":19"/>
+          <s v=":20"/>
+          <s v=":21"/>
+          <s v=":22"/>
+          <s v=":23"/>
+          <s v=":24"/>
+          <s v=":25"/>
+          <s v=":26"/>
+          <s v=":27"/>
+          <s v=":28"/>
+          <s v=":29"/>
+          <s v=":30"/>
+          <s v=":31"/>
+          <s v=":32"/>
+          <s v=":33"/>
+          <s v=":34"/>
+          <s v=":35"/>
+          <s v=":36"/>
+          <s v=":37"/>
+          <s v=":38"/>
+          <s v=":39"/>
+          <s v=":40"/>
+          <s v=":41"/>
+          <s v=":42"/>
+          <s v=":43"/>
+          <s v=":44"/>
+          <s v=":45"/>
+          <s v=":46"/>
+          <s v=":47"/>
+          <s v=":48"/>
+          <s v=":49"/>
+          <s v=":50"/>
+          <s v=":51"/>
+          <s v=":52"/>
+          <s v=":53"/>
+          <s v=":54"/>
+          <s v=":55"/>
+          <s v=":56"/>
+          <s v=":57"/>
+          <s v=":58"/>
+          <s v=":59"/>
+          <s v="&gt;1/0/1900"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Hours (Time to complete)" numFmtId="0" databaseField="0">
+      <fieldGroup base="3">
+        <rangePr groupBy="hours" startDate="1899-12-30T00:00:38" endDate="1899-12-30T00:04:12"/>
+        <groupItems count="26">
+          <s v="&lt;1/0/1900"/>
+          <s v="12 AM"/>
+          <s v="1 AM"/>
+          <s v="2 AM"/>
+          <s v="3 AM"/>
+          <s v="4 AM"/>
+          <s v="5 AM"/>
+          <s v="6 AM"/>
+          <s v="7 AM"/>
+          <s v="8 AM"/>
+          <s v="9 AM"/>
+          <s v="10 AM"/>
+          <s v="11 AM"/>
+          <s v="12 PM"/>
+          <s v="1 PM"/>
+          <s v="2 PM"/>
+          <s v="3 PM"/>
+          <s v="4 PM"/>
+          <s v="5 PM"/>
+          <s v="6 PM"/>
+          <s v="7 PM"/>
+          <s v="8 PM"/>
+          <s v="9 PM"/>
+          <s v="10 PM"/>
+          <s v="11 PM"/>
+          <s v="&gt;1/0/1900"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -1763,9 +1823,9 @@
     <n v="1"/>
     <d v="2026-04-09T08:42:27"/>
     <d v="2026-04-09T08:43:07"/>
-    <d v="1899-12-30T00:00:40"/>
     <x v="0"/>
-    <m/>
+    <x v="0"/>
+    <x v="0"/>
     <m/>
     <x v="0"/>
     <x v="0"/>
@@ -1781,9 +1841,9 @@
     <n v="2"/>
     <d v="2026-04-09T09:31:46"/>
     <d v="2026-04-09T09:34:32"/>
-    <d v="1899-12-30T00:02:46"/>
+    <x v="1"/>
     <x v="0"/>
-    <m/>
+    <x v="0"/>
     <m/>
     <x v="1"/>
     <x v="0"/>
@@ -1799,9 +1859,9 @@
     <n v="3"/>
     <d v="2026-04-09T09:51:48"/>
     <d v="2026-04-09T09:53:37"/>
-    <d v="1899-12-30T00:01:49"/>
+    <x v="2"/>
     <x v="0"/>
-    <m/>
+    <x v="0"/>
     <m/>
     <x v="2"/>
     <x v="1"/>
@@ -1817,9 +1877,9 @@
     <n v="4"/>
     <d v="2026-04-09T11:46:05"/>
     <d v="2026-04-09T11:50:17"/>
-    <d v="1899-12-30T00:04:12"/>
+    <x v="3"/>
     <x v="0"/>
-    <m/>
+    <x v="0"/>
     <m/>
     <x v="2"/>
     <x v="1"/>
@@ -1835,9 +1895,9 @@
     <n v="5"/>
     <d v="2026-04-10T01:06:42"/>
     <d v="2026-04-10T01:07:20"/>
-    <d v="1899-12-30T00:00:38"/>
+    <x v="4"/>
     <x v="0"/>
-    <m/>
+    <x v="0"/>
     <m/>
     <x v="2"/>
     <x v="1"/>
@@ -1853,9 +1913,9 @@
     <n v="6"/>
     <d v="2026-04-12T07:30:59"/>
     <d v="2026-04-12T07:31:47"/>
-    <d v="1899-12-30T00:00:48"/>
+    <x v="5"/>
     <x v="0"/>
-    <m/>
+    <x v="0"/>
     <m/>
     <x v="2"/>
     <x v="0"/>
@@ -1871,9 +1931,9 @@
     <m/>
     <m/>
     <m/>
-    <d v="1899-12-30T00:01:49"/>
+    <x v="2"/>
     <x v="1"/>
-    <m/>
+    <x v="0"/>
     <m/>
     <x v="3"/>
     <x v="2"/>
@@ -1889,13 +1949,23 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9DDABD87-8AD0-4DA5-BB0F-F7375C37BFEC}" name="PivotTable3" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
-  <location ref="A1:B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9DDABD87-8AD0-4DA5-BB0F-F7375C37BFEC}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="33">
+  <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="45" showAll="0"/>
+    <pivotField numFmtId="45" showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0">
       <items count="3">
         <item x="0"/>
@@ -1903,18 +1973,23 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="1"/>
         <item x="2"/>
         <item x="0"/>
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField dataField="1" showAll="0">
       <items count="4">
         <item x="0"/>
         <item x="2"/>
@@ -1938,7 +2013,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="4">
         <item x="0"/>
         <item x="1"/>
@@ -1956,16 +2031,184 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="63">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="63">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="27">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="12"/>
+    <field x="7"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -1975,10 +2218,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of How often do you visit Lola's kitchen? " fld="7" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of How would you rate your overall experience today?" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="0" format="11" series="1">
+    <chartFormat chart="0" format="20" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -2324,16 +2567,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F765A2F2-A0FF-4A50-8BC3-45E9060A7F8B}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="68.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B1" t="s">
@@ -2341,27 +2584,35 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
+      <c r="A2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="9">
         <v>4</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="7">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2">
-        <v>5</v>
+      <c r="A3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="9">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2">
-        <v>6</v>
+      <c r="B5" s="9">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2376,8 +2627,8 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="3" customWidth="1"/>
+    <col min="2" max="3" width="20" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="2" customWidth="1"/>
     <col min="5" max="7" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="13" width="20" bestFit="1" customWidth="1"/>
@@ -2390,13 +2641,13 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E1" t="s">
@@ -2440,13 +2691,13 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>46121.362812500003</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>46121.363275463002</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <f t="shared" ref="D2:D7" si="0">C2-B2</f>
         <v>4.6296299842651933E-4</v>
       </c>
@@ -2486,13 +2737,13 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>46121.397060185198</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>46121.3989814815</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <f t="shared" si="0"/>
         <v>1.9212963015888818E-3</v>
       </c>
@@ -2532,13 +2783,13 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>46121.410972222198</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>46121.412233796298</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <f t="shared" si="0"/>
         <v>1.2615740997716784E-3</v>
       </c>
@@ -2578,13 +2829,13 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>46121.490335648101</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>46121.493252314802</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <f t="shared" si="0"/>
         <v>2.9166667009121738E-3</v>
       </c>
@@ -2624,13 +2875,13 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>46122.046319444402</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>46122.046759259298</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>4.3981489579891786E-4</v>
       </c>
@@ -2670,13 +2921,13 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>46124.313182870399</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>46124.313738425903</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>5.5555550352437422E-4</v>
       </c>
@@ -2713,59 +2964,49 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <f>AVERAGE(D2:D7)</f>
         <v>1.2596450833370909E-3</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2">
+      <c r="I8">
         <f>AVERAGE(I2:I7)</f>
         <v>4.5</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2">
+      <c r="K8">
         <f>AVERAGE(_xlfn.SWITCH("SATISFIED",0,"VERY SATISFIED","1"))</f>
         <v>1</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <f>COUNTIF(H2:H7, "Weekly")</f>
         <v>1</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <f>COUNTIF(H2:H7,"Monthly")</f>
         <v>1</v>
       </c>
-      <c r="E17" s="8"/>
+      <c r="E17" s="7"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <f>COUNTIF(H2:H7,"This Is My First Visit")</f>
         <v>4</v>
       </c>
-      <c r="E18" s="8"/>
+      <c r="E18" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
